--- a/output/2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale. Sede reale: Kajang, Selangor. Produttore/fornitore di sistemi anti-inquinamento (dust collector, cicloni, spray booth, AHU); agente esclusivo CORAL S.p.A. (Italia) in Malesia. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Verificato via WebFetch sul sito ufficiale. Sede reale: Kajang, Selangor. Produttore/fornitore di sistemi anti-inquinamento (dust collector, cicloni, spray booth, AHU); agente esclusivo CORAL S.p.A. (Italia) in Malesia. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale. Sede reale: Shah Alam, Selangor. Fondata nel 2002 (nome da Dust, Air and Vacuum); dust collector a sacchi/cartuccia/multiciclone, blower centrifughi, trasportatori pneumatici. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Verificato via WebFetch sul sito ufficiale. Sede reale: Shah Alam, Selangor. Fondata nel 2002 (nome da Dust, Air and Vacuum); dust collector a sacchi/cartuccia/multiciclone, blower centrifughi, trasportatori pneumatici. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale. Sede reale: Seri Kembangan, Selangor. Ventilazione industriale (exhaust fan, blower, HVLS) per estrazione di calore/fumi/polvere/umidità, oltre 300 impianti serviti dal 2006. Attenzione: prodotto principale è ventilazione generale, non filtrazione/captazione polveri dedicata - pertinenza al settore depolverazione da confermare in sede di contatto commerciale. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Verificato via WebFetch sul sito ufficiale. Sede reale: Seri Kembangan, Selangor. Ventilazione industriale (exhaust fan, blower, HVLS) per estrazione di calore/fumi/polvere/umidità, oltre 300 impianti serviti dal 2006. Attenzione: prodotto principale è ventilazione generale, non filtrazione/captazione polveri dedicata - pertinenza al settore depolverazione da confermare in sede di contatto commerciale. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sito ufficiale protetto da anti-bot (WebFetch bloccato da verifica browser); esistenza e prodotti confermati tramite WebSearch su fonti terze (infopages.net.my, airpollutioncontrol.com.my) che citano Master Jaya Corporation Sdn Bhd (Reg. 332530-K), Seri Kembangan, Selangor, 27+ anni di esperienza in cicloni, bag filter dust collector, gas scrubber. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Sito ufficiale protetto da anti-bot (WebFetch bloccato da verifica browser); esistenza e prodotti confermati tramite WebSearch su fonti terze (infopages.net.my, airpollutioncontrol.com.my) che citano Master Jaya Corporation Sdn Bhd (Reg. 332530-K), Seri Kembangan, Selangor, 27+ anni di esperienza in cicloni, bag filter dust collector, gas scrubber. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale e WebSearch di conferma (Reg. 202101023225). Sede reale: Senai, Johor Bahru, Johor. Produttore/fornitore diversificato di attrezzature industriali (laser, robotica, forni, pulitori ad ultrasuoni); i sistemi di purificazione/depolverazione aria sono una delle numerose linee di prodotto, non il core business esclusivo. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Verificato via WebFetch sul sito ufficiale e WebSearch di conferma (Reg. 202101023225). Sede reale: Senai, Johor Bahru, Johor. Produttore/fornitore diversificato di attrezzature industriali (laser, robotica, forni, pulitori ad ultrasuoni); i sistemi di purificazione/depolverazione aria sono una delle numerose linee di prodotto, non il core business esclusivo. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -876,7 +876,6 @@
           <t>+60-72342307</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Verificato via WebFetch sul sito ufficiale (Reg. 201701045716). Sede reale: Johor Bahru, Johor. Societa' di ingegneria M&amp;E con dust collector system tra i servizi offerti (insieme a ACMV, clean room, fire system). Email non trovata/non verificabile, lasciata vuota. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
@@ -926,7 +925,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1046,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sito ufficiale non accessibile via WebFetch (errore 403); esistenza e dati confermati tramite WebSearch su fonti terze (yellowpages.my, infopages.net.my, keepital.com). Sede: Shah Alam, Selangor. Produttore di filtri per dust collector (sacchi, cartucce, gabbie filtro) da oltre 25 anni. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Sito ufficiale non accessibile via WebFetch (errore 403); esistenza e dati confermati tramite WebSearch su fonti terze (yellowpages.my, infopages.net.my, keepital.com). Sede: Shah Alam, Selangor. Produttore di filtri per dust collector (sacchi, cartucce, gabbie filtro) da oltre 25 anni. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1235,14 +1234,11 @@
           <t>https://airfilterengineering.my/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>SCARTATO - fuori settore: dal sito ufficiale risulta specializzata esclusivamente in aria compressa e gas purificati (essiccatori, filtri aria compressa, separatori acqua/umidita', generatori di azoto); nessun riferimento a dust collection/depolverazione industriale.</t>
@@ -1265,14 +1261,11 @@
           <t>https://filtrationexpert.com.my/</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>SCARTATO - fuori settore: dal sito ufficiale risulta specializzata in filtrazione di oli lubrificanti/idraulici e aria compressa (essiccatori); nessun collegamento con sistemi di raccolta polveri (dust collection) riscontrato.</t>
@@ -1295,14 +1288,11 @@
           <t>https://aircaretechnology.com.my/</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>SCARTATO - fuori settore: dal sito ufficiale risulta specializzata esclusivamente in aria compressa (compressori industriali, filtri coalescenti, essiccatori, separatori olio-acqua); il sito stesso non menziona alcuna attivita' di dust collection/depolverazione.</t>

--- a/output/2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale. Due sedi Malesia: Johor Bahru, Johor e Pelabuhan Klang, Selangor (oltre a sede Singapore). Dust/fume/mist collector, carboni attivi. Email decodificata da protezione anti-spam Cloudflare presente sul sito ufficiale (dominio coerente: gee-as.com). Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Verificato via WebFetch sul sito ufficiale. Due sedi Malesia: Johor Bahru, Johor e Pelabuhan Klang, Selangor (oltre a sede Singapore). Dust/fume/mist collector, carboni attivi. Email decodificata da protezione anti-spam Cloudflare presente sul sito ufficiale (dominio coerente: gee-as.com). Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sul sito ufficiale (Reg. 201701045716). Sede reale: Johor Bahru, Johor. Societa' di ingegneria M&amp;E con dust collector system tra i servizi offerti (insieme a ACMV, clean room, fire system). Email non trovata/non verificabile, lasciata vuota. Copertura nazionale plausibile, non sede locale in Kelantan.</t>
+          <t>Verificato via WebFetch sul sito ufficiale (Reg. 201701045716). Sede reale: Johor Bahru, Johor. Societa' di ingegneria M&amp;E con dust collector system tra i servizi offerti (insieme a ACMV, clean room, fire system). Email non trovata/non verificabile, lasciata vuota. Copertura nazionale plausibile, non sede locale in Kelantan. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
